--- a/outputs/Wage_(non-qualified_labour,_non-agricultural)_tukey_classification_matrix.xlsx
+++ b/outputs/Wage_(non-qualified_labour,_non-agricultural)_tukey_classification_matrix.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2550" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2550" uniqueCount="124">
   <si>
     <t>2020 May</t>
   </si>
@@ -347,6 +347,9 @@
   </si>
   <si>
     <t>Alarm</t>
+  </si>
+  <si>
+    <t>No data</t>
   </si>
   <si>
     <t>0%</t>
@@ -1210,13 +1213,13 @@
         <v>108</v>
       </c>
       <c r="BU2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BV2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BW2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="3" spans="1:75">
@@ -1437,13 +1440,13 @@
         <v>108</v>
       </c>
       <c r="BU3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BV3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BW3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="4" spans="1:75">
@@ -1664,13 +1667,13 @@
         <v>108</v>
       </c>
       <c r="BU4" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BV4" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BW4" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="5" spans="1:75">
@@ -1891,13 +1894,13 @@
         <v>108</v>
       </c>
       <c r="BU5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BV5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BW5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="6" spans="1:75">
@@ -2118,13 +2121,13 @@
         <v>109</v>
       </c>
       <c r="BU6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="BV6" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="BW6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="7" spans="1:75">
@@ -2303,7 +2306,7 @@
         <v>108</v>
       </c>
       <c r="BG7" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="BH7" t="s">
         <v>108</v>
@@ -2345,13 +2348,13 @@
         <v>108</v>
       </c>
       <c r="BU7" t="s">
+        <v>114</v>
+      </c>
+      <c r="BV7" t="s">
         <v>113</v>
       </c>
-      <c r="BV7" t="s">
-        <v>112</v>
-      </c>
       <c r="BW7" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="8" spans="1:75">
@@ -2572,13 +2575,13 @@
         <v>108</v>
       </c>
       <c r="BU8" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BV8" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BW8" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="9" spans="1:75">
@@ -2799,13 +2802,13 @@
         <v>108</v>
       </c>
       <c r="BU9" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="BV9" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BW9" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="10" spans="1:75">
@@ -3026,13 +3029,13 @@
         <v>108</v>
       </c>
       <c r="BU10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BV10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BW10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="11" spans="1:75">
@@ -3253,13 +3256,13 @@
         <v>108</v>
       </c>
       <c r="BU11" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="BV11" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="BW11" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="12" spans="1:75">
@@ -3480,13 +3483,13 @@
         <v>108</v>
       </c>
       <c r="BU12" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BV12" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="BW12" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="13" spans="1:75">
@@ -3707,13 +3710,13 @@
         <v>108</v>
       </c>
       <c r="BU13" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BV13" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BW13" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="14" spans="1:75">
@@ -3934,13 +3937,13 @@
         <v>108</v>
       </c>
       <c r="BU14" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BV14" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BW14" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="15" spans="1:75">
@@ -4161,13 +4164,13 @@
         <v>108</v>
       </c>
       <c r="BU15" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BV15" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BW15" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16" spans="1:75">
@@ -4388,13 +4391,13 @@
         <v>108</v>
       </c>
       <c r="BU16" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BV16" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BW16" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="17" spans="1:75">
@@ -4615,13 +4618,13 @@
         <v>108</v>
       </c>
       <c r="BU17" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BV17" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BW17" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="18" spans="1:75">
@@ -4842,13 +4845,13 @@
         <v>108</v>
       </c>
       <c r="BU18" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BV18" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BW18" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="19" spans="1:75">
@@ -5069,13 +5072,13 @@
         <v>108</v>
       </c>
       <c r="BU19" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="BV19" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="BW19" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="20" spans="1:75">
@@ -5296,13 +5299,13 @@
         <v>108</v>
       </c>
       <c r="BU20" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BV20" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BW20" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="21" spans="1:75">
@@ -5523,13 +5526,13 @@
         <v>108</v>
       </c>
       <c r="BU21" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="BV21" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="BW21" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="22" spans="1:75">
@@ -5750,13 +5753,13 @@
         <v>108</v>
       </c>
       <c r="BU22" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BV22" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BW22" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="23" spans="1:75">
@@ -5977,13 +5980,13 @@
         <v>108</v>
       </c>
       <c r="BU23" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BV23" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BW23" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="24" spans="1:75">
@@ -6204,13 +6207,13 @@
         <v>108</v>
       </c>
       <c r="BU24" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BV24" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BW24" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="25" spans="1:75">
@@ -6431,13 +6434,13 @@
         <v>110</v>
       </c>
       <c r="BU25" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="BV25" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BW25" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="26" spans="1:75">
@@ -6658,13 +6661,13 @@
         <v>108</v>
       </c>
       <c r="BU26" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BV26" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BW26" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="27" spans="1:75">
@@ -6885,13 +6888,13 @@
         <v>108</v>
       </c>
       <c r="BU27" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BV27" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BW27" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="28" spans="1:75">
@@ -7112,13 +7115,13 @@
         <v>108</v>
       </c>
       <c r="BU28" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BV28" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BW28" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="29" spans="1:75">
@@ -7339,13 +7342,13 @@
         <v>108</v>
       </c>
       <c r="BU29" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BV29" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BW29" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="30" spans="1:75">
@@ -7566,13 +7569,13 @@
         <v>108</v>
       </c>
       <c r="BU30" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BV30" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BW30" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="31" spans="1:75">
@@ -7793,13 +7796,13 @@
         <v>108</v>
       </c>
       <c r="BU31" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BV31" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BW31" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="32" spans="1:75">
@@ -8020,13 +8023,13 @@
         <v>108</v>
       </c>
       <c r="BU32" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="BV32" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BW32" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="33" spans="1:75">
@@ -8247,13 +8250,13 @@
         <v>108</v>
       </c>
       <c r="BU33" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BV33" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BW33" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="34" spans="1:75">
@@ -8474,13 +8477,13 @@
         <v>108</v>
       </c>
       <c r="BU34" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BV34" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="BW34" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/Wage_(non-qualified_labour,_non-agricultural)_tukey_classification_matrix.xlsx
+++ b/outputs/Wage_(non-qualified_labour,_non-agricultural)_tukey_classification_matrix.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2550" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2550" uniqueCount="111">
   <si>
     <t>2020 May</t>
   </si>
@@ -343,49 +343,10 @@
     <t>Minimal</t>
   </si>
   <si>
-    <t>Alert</t>
-  </si>
-  <si>
-    <t>Alarm</t>
-  </si>
-  <si>
     <t>No data</t>
   </si>
   <si>
     <t>0%</t>
-  </si>
-  <si>
-    <t>1%</t>
-  </si>
-  <si>
-    <t>8%</t>
-  </si>
-  <si>
-    <t>6%</t>
-  </si>
-  <si>
-    <t>11%</t>
-  </si>
-  <si>
-    <t>4%</t>
-  </si>
-  <si>
-    <t>32%</t>
-  </si>
-  <si>
-    <t>24%</t>
-  </si>
-  <si>
-    <t>3%</t>
-  </si>
-  <si>
-    <t>10%</t>
-  </si>
-  <si>
-    <t>7%</t>
-  </si>
-  <si>
-    <t>14%</t>
   </si>
 </sst>
 </file>
@@ -1213,13 +1174,13 @@
         <v>108</v>
       </c>
       <c r="BU2" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="BV2" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="BW2" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="3" spans="1:75">
@@ -1440,13 +1401,13 @@
         <v>108</v>
       </c>
       <c r="BU3" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="BV3" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="BW3" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="4" spans="1:75">
@@ -1667,13 +1628,13 @@
         <v>108</v>
       </c>
       <c r="BU4" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="BV4" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="BW4" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="5" spans="1:75">
@@ -1684,13 +1645,13 @@
         <v>108</v>
       </c>
       <c r="C5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F5" t="s">
         <v>108</v>
@@ -1720,13 +1681,13 @@
         <v>108</v>
       </c>
       <c r="O5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="P5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="Q5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="R5" t="s">
         <v>108</v>
@@ -1756,13 +1717,13 @@
         <v>108</v>
       </c>
       <c r="AA5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AB5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AC5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AD5" t="s">
         <v>108</v>
@@ -1792,13 +1753,13 @@
         <v>108</v>
       </c>
       <c r="AM5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AN5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AO5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AP5" t="s">
         <v>108</v>
@@ -1828,13 +1789,13 @@
         <v>108</v>
       </c>
       <c r="AY5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AZ5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BA5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BB5" t="s">
         <v>108</v>
@@ -1864,13 +1825,13 @@
         <v>108</v>
       </c>
       <c r="BK5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BL5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BM5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BN5" t="s">
         <v>108</v>
@@ -1894,13 +1855,13 @@
         <v>108</v>
       </c>
       <c r="BU5" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="BV5" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="BW5" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="6" spans="1:75">
@@ -2076,16 +2037,16 @@
         <v>108</v>
       </c>
       <c r="BF6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BG6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BH6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BI6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BJ6" t="s">
         <v>108</v>
@@ -2112,22 +2073,22 @@
         <v>108</v>
       </c>
       <c r="BR6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BS6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BT6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BU6" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="BV6" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="BW6" t="s">
-        <v>121</v>
+        <v>110</v>
       </c>
     </row>
     <row r="7" spans="1:75">
@@ -2144,25 +2105,25 @@
         <v>108</v>
       </c>
       <c r="E7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F7" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="G7" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="H7" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="I7" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="J7" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="K7" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="L7" t="s">
         <v>108</v>
@@ -2306,7 +2267,7 @@
         <v>108</v>
       </c>
       <c r="BG7" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="BH7" t="s">
         <v>108</v>
@@ -2348,13 +2309,13 @@
         <v>108</v>
       </c>
       <c r="BU7" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="BV7" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="BW7" t="s">
-        <v>121</v>
+        <v>110</v>
       </c>
     </row>
     <row r="8" spans="1:75">
@@ -2575,13 +2536,13 @@
         <v>108</v>
       </c>
       <c r="BU8" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="BV8" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="BW8" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="9" spans="1:75">
@@ -2742,22 +2703,22 @@
         <v>108</v>
       </c>
       <c r="BA9" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BB9" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BC9" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BD9" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BE9" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BF9" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BG9" t="s">
         <v>108</v>
@@ -2802,13 +2763,13 @@
         <v>108</v>
       </c>
       <c r="BU9" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="BV9" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="BW9" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
     </row>
     <row r="10" spans="1:75">
@@ -3029,13 +2990,13 @@
         <v>108</v>
       </c>
       <c r="BU10" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="BV10" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="BW10" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="11" spans="1:75">
@@ -3178,7 +3139,7 @@
         <v>108</v>
       </c>
       <c r="AU11" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AV11" t="s">
         <v>108</v>
@@ -3199,13 +3160,13 @@
         <v>108</v>
       </c>
       <c r="BB11" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BC11" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BD11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BE11" t="s">
         <v>108</v>
@@ -3214,7 +3175,7 @@
         <v>108</v>
       </c>
       <c r="BG11" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BH11" t="s">
         <v>108</v>
@@ -3256,13 +3217,13 @@
         <v>108</v>
       </c>
       <c r="BU11" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="BV11" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="BW11" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
     </row>
     <row r="12" spans="1:75">
@@ -3270,7 +3231,7 @@
         <v>85</v>
       </c>
       <c r="B12" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C12" t="s">
         <v>108</v>
@@ -3483,13 +3444,13 @@
         <v>108</v>
       </c>
       <c r="BU12" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="BV12" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="BW12" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
     </row>
     <row r="13" spans="1:75">
@@ -3710,13 +3671,13 @@
         <v>108</v>
       </c>
       <c r="BU13" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="BV13" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="BW13" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="14" spans="1:75">
@@ -3937,13 +3898,13 @@
         <v>108</v>
       </c>
       <c r="BU14" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="BV14" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="BW14" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="15" spans="1:75">
@@ -4164,13 +4125,13 @@
         <v>108</v>
       </c>
       <c r="BU15" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="BV15" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="BW15" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="16" spans="1:75">
@@ -4199,19 +4160,19 @@
         <v>108</v>
       </c>
       <c r="I16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="J16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="K16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="L16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="M16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="N16" t="s">
         <v>108</v>
@@ -4235,19 +4196,19 @@
         <v>108</v>
       </c>
       <c r="U16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="V16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="W16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="X16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="Y16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="Z16" t="s">
         <v>108</v>
@@ -4271,19 +4232,19 @@
         <v>108</v>
       </c>
       <c r="AG16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AH16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AI16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AJ16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AK16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AL16" t="s">
         <v>108</v>
@@ -4307,19 +4268,19 @@
         <v>108</v>
       </c>
       <c r="AS16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AT16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AU16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AV16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AW16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AX16" t="s">
         <v>108</v>
@@ -4343,19 +4304,19 @@
         <v>108</v>
       </c>
       <c r="BE16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BF16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BG16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BH16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BI16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BJ16" t="s">
         <v>108</v>
@@ -4379,25 +4340,25 @@
         <v>108</v>
       </c>
       <c r="BQ16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BR16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BS16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BT16" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BU16" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="BV16" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="BW16" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="17" spans="1:75">
@@ -4618,13 +4579,13 @@
         <v>108</v>
       </c>
       <c r="BU17" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="BV17" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="BW17" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="18" spans="1:75">
@@ -4641,28 +4602,28 @@
         <v>108</v>
       </c>
       <c r="E18" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F18" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="G18" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H18" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="I18" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="J18" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="K18" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="L18" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="M18" t="s">
         <v>108</v>
@@ -4677,28 +4638,28 @@
         <v>108</v>
       </c>
       <c r="Q18" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="R18" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="S18" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="T18" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="U18" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="V18" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="W18" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="X18" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="Y18" t="s">
         <v>108</v>
@@ -4713,28 +4674,28 @@
         <v>108</v>
       </c>
       <c r="AC18" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AD18" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AE18" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AF18" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AG18" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AH18" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AI18" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AJ18" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AK18" t="s">
         <v>108</v>
@@ -4749,28 +4710,28 @@
         <v>108</v>
       </c>
       <c r="AO18" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AP18" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AQ18" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AR18" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AS18" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AT18" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AU18" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AV18" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AW18" t="s">
         <v>108</v>
@@ -4785,28 +4746,28 @@
         <v>108</v>
       </c>
       <c r="BA18" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BB18" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BC18" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BD18" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BE18" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BF18" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BG18" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BH18" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BI18" t="s">
         <v>108</v>
@@ -4821,37 +4782,37 @@
         <v>108</v>
       </c>
       <c r="BM18" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BN18" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BO18" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BP18" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BQ18" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BR18" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BS18" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BT18" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BU18" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="BV18" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="BW18" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="19" spans="1:75">
@@ -4988,22 +4949,22 @@
         <v>108</v>
       </c>
       <c r="AS19" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AT19" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AU19" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AV19" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AW19" t="s">
         <v>108</v>
       </c>
       <c r="AX19" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AY19" t="s">
         <v>108</v>
@@ -5024,22 +4985,22 @@
         <v>108</v>
       </c>
       <c r="BE19" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BF19" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BG19" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BH19" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BI19" t="s">
         <v>108</v>
       </c>
       <c r="BJ19" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="BK19" t="s">
         <v>108</v>
@@ -5072,13 +5033,13 @@
         <v>108</v>
       </c>
       <c r="BU19" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="BV19" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="BW19" t="s">
-        <v>123</v>
+        <v>110</v>
       </c>
     </row>
     <row r="20" spans="1:75">
@@ -5299,13 +5260,13 @@
         <v>108</v>
       </c>
       <c r="BU20" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="BV20" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="BW20" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="21" spans="1:75">
@@ -5403,13 +5364,13 @@
         <v>108</v>
       </c>
       <c r="AF21" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AG21" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AH21" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AI21" t="s">
         <v>108</v>
@@ -5421,7 +5382,7 @@
         <v>108</v>
       </c>
       <c r="AL21" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AM21" t="s">
         <v>108</v>
@@ -5463,7 +5424,7 @@
         <v>108</v>
       </c>
       <c r="AZ21" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BA21" t="s">
         <v>108</v>
@@ -5526,13 +5487,13 @@
         <v>108</v>
       </c>
       <c r="BU21" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="BV21" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="BW21" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
     </row>
     <row r="22" spans="1:75">
@@ -5540,226 +5501,226 @@
         <v>95</v>
       </c>
       <c r="B22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="G22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="I22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="J22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="K22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="L22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="M22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="N22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="O22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="P22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="Q22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="R22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="S22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="T22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="U22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="V22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="W22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="X22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="Y22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="Z22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AA22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AB22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AC22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AD22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AE22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AF22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AG22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AH22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AI22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AJ22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AK22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AL22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AM22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AN22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AO22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AP22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AQ22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AR22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AS22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AT22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AU22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AV22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AW22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AX22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AY22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AZ22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BA22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BB22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BC22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BD22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BE22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BF22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BG22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BH22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BI22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BJ22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BK22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BL22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BM22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BN22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BO22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BP22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BQ22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BR22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BS22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BT22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BU22" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="BV22" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="BW22" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="23" spans="1:75">
@@ -5980,13 +5941,13 @@
         <v>108</v>
       </c>
       <c r="BU23" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="BV23" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="BW23" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="24" spans="1:75">
@@ -5997,13 +5958,13 @@
         <v>108</v>
       </c>
       <c r="C24" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D24" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E24" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F24" t="s">
         <v>108</v>
@@ -6033,13 +5994,13 @@
         <v>108</v>
       </c>
       <c r="O24" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="P24" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="Q24" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="R24" t="s">
         <v>108</v>
@@ -6069,13 +6030,13 @@
         <v>108</v>
       </c>
       <c r="AA24" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AB24" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AC24" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AD24" t="s">
         <v>108</v>
@@ -6105,13 +6066,13 @@
         <v>108</v>
       </c>
       <c r="AM24" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AN24" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AO24" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AP24" t="s">
         <v>108</v>
@@ -6141,13 +6102,13 @@
         <v>108</v>
       </c>
       <c r="AY24" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AZ24" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BA24" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BB24" t="s">
         <v>108</v>
@@ -6177,13 +6138,13 @@
         <v>108</v>
       </c>
       <c r="BK24" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BL24" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BM24" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="BN24" t="s">
         <v>108</v>
@@ -6207,13 +6168,13 @@
         <v>108</v>
       </c>
       <c r="BU24" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="BV24" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="BW24" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="25" spans="1:75">
@@ -6362,85 +6323,85 @@
         <v>108</v>
       </c>
       <c r="AW25" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AX25" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AY25" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AZ25" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BA25" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BB25" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BC25" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BD25" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BE25" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BF25" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BG25" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BH25" t="s">
         <v>108</v>
       </c>
       <c r="BI25" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BJ25" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BK25" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BL25" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BM25" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BN25" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BO25" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BP25" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BQ25" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BR25" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BS25" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BT25" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BU25" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="BV25" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="BW25" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
     </row>
     <row r="26" spans="1:75">
@@ -6661,13 +6622,13 @@
         <v>108</v>
       </c>
       <c r="BU26" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="BV26" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="BW26" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="27" spans="1:75">
@@ -6888,13 +6849,13 @@
         <v>108</v>
       </c>
       <c r="BU27" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="BV27" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="BW27" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="28" spans="1:75">
@@ -7115,13 +7076,13 @@
         <v>108</v>
       </c>
       <c r="BU28" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="BV28" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="BW28" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="29" spans="1:75">
@@ -7342,13 +7303,13 @@
         <v>108</v>
       </c>
       <c r="BU29" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="BV29" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="BW29" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="30" spans="1:75">
@@ -7569,13 +7530,13 @@
         <v>108</v>
       </c>
       <c r="BU30" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="BV30" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="BW30" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="31" spans="1:75">
@@ -7796,13 +7757,13 @@
         <v>108</v>
       </c>
       <c r="BU31" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="BV31" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="BW31" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="32" spans="1:75">
@@ -7918,61 +7879,61 @@
         <v>108</v>
       </c>
       <c r="AL32" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AM32" t="s">
         <v>108</v>
       </c>
       <c r="AN32" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AO32" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AP32" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AQ32" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AR32" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AS32" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AT32" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AU32" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AV32" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AW32" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AX32" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AY32" t="s">
         <v>108</v>
       </c>
       <c r="AZ32" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BA32" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BB32" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BC32" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BD32" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="BE32" t="s">
         <v>108</v>
@@ -8023,13 +7984,13 @@
         <v>108</v>
       </c>
       <c r="BU32" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="BV32" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="BW32" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
     </row>
     <row r="33" spans="1:75">
@@ -8250,13 +8211,13 @@
         <v>108</v>
       </c>
       <c r="BU33" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="BV33" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="BW33" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="34" spans="1:75">
@@ -8477,13 +8438,13 @@
         <v>108</v>
       </c>
       <c r="BU34" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="BV34" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="BW34" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/Wage_(non-qualified_labour,_non-agricultural)_tukey_classification_matrix.xlsx
+++ b/outputs/Wage_(non-qualified_labour,_non-agricultural)_tukey_classification_matrix.xlsx
@@ -340,7 +340,7 @@
     <t>Zabul</t>
   </si>
   <si>
-    <t>Minimal</t>
+    <t>No concern</t>
   </si>
   <si>
     <t>No data</t>
